--- a/data/trans_dic/P34B01_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,7; 29,62</t>
+          <t>21,81; 29,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,57; 53,81</t>
+          <t>43,46; 53,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,18; 66,05</t>
+          <t>47,21; 64,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,16; 46,3</t>
+          <t>36,63; 45,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,4; 57,68</t>
+          <t>47,91; 57,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,72; 69,86</t>
+          <t>55,04; 70,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,25; 36,45</t>
+          <t>30,06; 36,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,21; 54,31</t>
+          <t>47,07; 53,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,47; 64,87</t>
+          <t>53,15; 65,31</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,82; 36,07</t>
+          <t>28,75; 35,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,61; 57,76</t>
+          <t>49,58; 57,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,43; 67,69</t>
+          <t>54,87; 66,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,78; 56,11</t>
+          <t>47,44; 56,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,44; 60,47</t>
+          <t>52,1; 60,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,24; 67,91</t>
+          <t>34,63; 68,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,36; 44,14</t>
+          <t>38,46; 44,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,5; 58,36</t>
+          <t>52,23; 57,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,68; 65,26</t>
+          <t>45,06; 65,14</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,55; 44,29</t>
+          <t>36,28; 44,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,07; 51,99</t>
+          <t>44,12; 51,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,98; 65,64</t>
+          <t>56,88; 65,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,19; 52,81</t>
+          <t>45,03; 52,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,86; 58,8</t>
+          <t>51,5; 58,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,9; 67,58</t>
+          <t>61,1; 67,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,0; 47,7</t>
+          <t>41,88; 47,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,86; 54,17</t>
+          <t>48,72; 54,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,85; 65,32</t>
+          <t>59,63; 65,14</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,63; 50,36</t>
+          <t>41,57; 50,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,22; 57,57</t>
+          <t>49,3; 57,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,36; 68,85</t>
+          <t>20,95; 68,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,07; 58,8</t>
+          <t>50,26; 58,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,35; 62,24</t>
+          <t>54,5; 62,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,32; 67,2</t>
+          <t>51,24; 67,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,26; 52,94</t>
+          <t>46,92; 53,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,89; 58,41</t>
+          <t>53,15; 58,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,59; 66,4</t>
+          <t>33,54; 66,12</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,86; 65,33</t>
+          <t>55,53; 65,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,85; 66,93</t>
+          <t>57,97; 67,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,86; 69,28</t>
+          <t>61,81; 69,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,41; 61,1</t>
+          <t>51,0; 60,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,59; 56,69</t>
+          <t>46,77; 55,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,27; 67,41</t>
+          <t>61,26; 67,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,71; 61,55</t>
+          <t>54,96; 62,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,58; 60,35</t>
+          <t>53,55; 60,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62,72; 67,76</t>
+          <t>62,65; 67,53</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,69; 73,81</t>
+          <t>63,14; 74,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57,24; 68,26</t>
+          <t>57,16; 67,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,61; 79,14</t>
+          <t>72,19; 79,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46,07; 56,91</t>
+          <t>46,28; 56,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,18; 60,65</t>
+          <t>49,97; 60,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,33; 89,93</t>
+          <t>63,55; 90,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,7; 63,69</t>
+          <t>55,69; 63,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55,27; 62,91</t>
+          <t>55,03; 62,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69,12; 87,42</t>
+          <t>69,01; 88,23</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,39; 69,3</t>
+          <t>56,4; 69,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,26; 60,94</t>
+          <t>49,59; 60,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58,21; 66,65</t>
+          <t>58,01; 67,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,03; 43,3</t>
+          <t>33,39; 43,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,12; 44,64</t>
+          <t>34,34; 45,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,64; 44,14</t>
+          <t>37,53; 44,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,69; 52,4</t>
+          <t>43,69; 51,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,26; 49,45</t>
+          <t>41,16; 49,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46,58; 52,28</t>
+          <t>46,57; 52,48</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,75; 46,36</t>
+          <t>42,7; 46,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,55; 55,84</t>
+          <t>52,44; 56,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,47; 65,07</t>
+          <t>45,4; 65,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47,55; 51,04</t>
+          <t>47,76; 51,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,75; 55,08</t>
+          <t>51,57; 55,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,4; 68,48</t>
+          <t>58,54; 69,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,82; 48,31</t>
+          <t>45,71; 48,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>52,55; 55,02</t>
+          <t>52,46; 54,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52,94; 64,75</t>
+          <t>53,76; 64,56</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98280; 134158</t>
+          <t>98787; 135267</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>182755; 225723</t>
+          <t>182297; 224142</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>194478; 261175</t>
+          <t>186683; 255943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159856; 199203</t>
+          <t>157600; 197345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>187582; 228276</t>
+          <t>189605; 227857</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>169325; 216205</t>
+          <t>170325; 217254</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>267175; 321913</t>
+          <t>265534; 322864</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>384877; 442709</t>
+          <t>383756; 438085</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>369883; 457299</t>
+          <t>374624; 460342</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>197793; 247519</t>
+          <t>197299; 245324</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>292953; 341085</t>
+          <t>292762; 341049</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>234135; 285924</t>
+          <t>231784; 282906</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>291566; 342438</t>
+          <t>289526; 342246</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>295532; 340799</t>
+          <t>293579; 339016</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>180257; 347376</t>
+          <t>177127; 348301</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>497368; 572190</t>
+          <t>498657; 571383</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>605824; 673489</t>
+          <t>602771; 669100</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>426598; 609513</t>
+          <t>420786; 608400</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>249223; 301965</t>
+          <t>247380; 302578</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>294862; 347864</t>
+          <t>295236; 347590</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>305521; 351933</t>
+          <t>304974; 351745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>320385; 374417</t>
+          <t>319230; 372599</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>336354; 388892</t>
+          <t>340639; 388847</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>327694; 363637</t>
+          <t>328775; 365505</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>584158; 663473</t>
+          <t>582503; 665301</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>650078; 720748</t>
+          <t>648153; 720051</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>642913; 701719</t>
+          <t>640550; 699793</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>255842; 309496</t>
+          <t>255505; 309739</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>317976; 371904</t>
+          <t>318482; 373339</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>188935; 609065</t>
+          <t>185285; 608129</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>308532; 362333</t>
+          <t>309686; 363232</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>352781; 404008</t>
+          <t>353757; 403804</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>376863; 475011</t>
+          <t>362197; 474822</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>569348; 651631</t>
+          <t>577547; 654255</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>685030; 756513</t>
+          <t>688423; 761923</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>502773; 1056722</t>
+          <t>533755; 1052195</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>239871; 280545</t>
+          <t>238444; 281656</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>276481; 319861</t>
+          <t>277067; 321889</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>345615; 387073</t>
+          <t>345355; 386316</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>230194; 273601</t>
+          <t>228384; 272411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>231470; 281671</t>
+          <t>232383; 278130</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>333173; 366556</t>
+          <t>333108; 366595</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>479943; 539915</t>
+          <t>482117; 544632</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>522290; 588227</t>
+          <t>522010; 587305</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>691526; 747081</t>
+          <t>690725; 744489</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>194207; 228664</t>
+          <t>195597; 229881</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>191376; 228207</t>
+          <t>191115; 227031</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>261910; 289466</t>
+          <t>264041; 289918</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>163095; 201454</t>
+          <t>163846; 201408</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>189562; 229131</t>
+          <t>188760; 229748</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>384957; 546661</t>
+          <t>386336; 551139</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>369722; 422766</t>
+          <t>369657; 423049</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>393595; 447966</t>
+          <t>391862; 447203</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>672946; 851190</t>
+          <t>671903; 859020</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>140890; 173150</t>
+          <t>140910; 174043</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>126590; 156624</t>
+          <t>127446; 155563</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>164586; 188453</t>
+          <t>164020; 190236</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>128479; 168433</t>
+          <t>129887; 168353</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>132525; 178643</t>
+          <t>137424; 181149</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>159591; 187179</t>
+          <t>159152; 186726</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>279112; 334739</t>
+          <t>279080; 330856</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>271141; 324979</t>
+          <t>270500; 326383</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>329236; 369478</t>
+          <t>329169; 370893</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1464067; 1587622</t>
+          <t>1462378; 1587521</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1783825; 1895308</t>
+          <t>1779993; 1901186</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1566737; 2242151</t>
+          <t>1564500; 2246886</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1690974; 1815026</t>
+          <t>1698472; 1820255</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1834306; 1952199</t>
+          <t>1827756; 1954278</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2126557; 2493674</t>
+          <t>2131832; 2518286</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3198768; 3372382</t>
+          <t>3190779; 3370581</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3646571; 3818082</t>
+          <t>3639807; 3809963</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3752286; 4588831</t>
+          <t>3810020; 4575706</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B01_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,81; 29,86</t>
+          <t>21,76; 29,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,46; 53,44</t>
+          <t>43,7; 53,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,21; 64,72</t>
+          <t>53,16; 68,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,63; 45,87</t>
+          <t>37,08; 46,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,91; 57,58</t>
+          <t>47,96; 57,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,04; 70,2</t>
+          <t>57,31; 71,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,06; 36,56</t>
+          <t>30,2; 36,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,07; 53,74</t>
+          <t>47,14; 54,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,15; 65,31</t>
+          <t>56,8; 67,61</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,75; 35,75</t>
+          <t>28,6; 35,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,58; 57,76</t>
+          <t>49,81; 57,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,87; 66,97</t>
+          <t>58,12; 69,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,44; 56,08</t>
+          <t>47,19; 55,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,1; 60,16</t>
+          <t>52,01; 60,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,63; 68,09</t>
+          <t>62,84; 71,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,46; 44,07</t>
+          <t>38,57; 44,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,23; 57,98</t>
+          <t>52,36; 57,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,06; 65,14</t>
+          <t>62,27; 69,19</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,01%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,28; 44,38</t>
+          <t>36,85; 44,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,12; 51,95</t>
+          <t>43,94; 52,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,88; 65,6</t>
+          <t>57,54; 65,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,03; 52,56</t>
+          <t>45,07; 52,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,5; 58,79</t>
+          <t>51,31; 58,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,1; 67,93</t>
+          <t>61,03; 67,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,88; 47,84</t>
+          <t>41,67; 47,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,72; 54,12</t>
+          <t>48,55; 54,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,63; 65,14</t>
+          <t>60,08; 65,59</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>67,12%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,57; 50,4</t>
+          <t>41,25; 49,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,3; 57,79</t>
+          <t>49,6; 57,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,95; 68,75</t>
+          <t>64,22; 71,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,26; 58,95</t>
+          <t>50,04; 58,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,5; 62,21</t>
+          <t>54,42; 62,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,24; 67,17</t>
+          <t>63,84; 69,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,92; 53,16</t>
+          <t>47,08; 53,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,15; 58,83</t>
+          <t>53,11; 59,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,54; 66,12</t>
+          <t>64,79; 69,34</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,53; 65,59</t>
+          <t>56,21; 65,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,97; 67,35</t>
+          <t>57,76; 66,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,81; 69,14</t>
+          <t>61,98; 69,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,0; 60,83</t>
+          <t>50,66; 61,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,77; 55,98</t>
+          <t>46,93; 56,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,26; 67,42</t>
+          <t>61,65; 67,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,96; 62,09</t>
+          <t>55,13; 61,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,55; 60,25</t>
+          <t>53,7; 60,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62,65; 67,53</t>
+          <t>62,9; 67,58</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,14; 74,21</t>
+          <t>63,14; 74,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57,16; 67,91</t>
+          <t>56,99; 68,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,26</t>
+          <t>71,85; 79,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46,28; 56,9</t>
+          <t>46,19; 57,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,97; 60,82</t>
+          <t>50,76; 60,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,55; 90,66</t>
+          <t>60,48; 67,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,69; 63,73</t>
+          <t>55,41; 63,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55,03; 62,8</t>
+          <t>55,35; 63,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69,01; 88,23</t>
+          <t>67,38; 72,25</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,4; 69,66</t>
+          <t>56,69; 69,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,59; 60,53</t>
+          <t>49,13; 60,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58,01; 67,28</t>
+          <t>58,5; 67,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,39; 43,28</t>
+          <t>33,15; 43,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,34; 45,27</t>
+          <t>33,92; 44,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,53; 44,04</t>
+          <t>37,53; 44,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,69; 51,79</t>
+          <t>43,75; 52,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,16; 49,67</t>
+          <t>41,58; 50,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46,57; 52,48</t>
+          <t>47,0; 52,47</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,7; 46,35</t>
+          <t>42,89; 46,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,44; 56,01</t>
+          <t>52,47; 55,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,4; 65,21</t>
+          <t>63,82; 67,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47,76; 51,18</t>
+          <t>47,71; 51,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,57; 55,13</t>
+          <t>51,73; 55,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,54; 69,15</t>
+          <t>61,12; 63,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,71; 48,28</t>
+          <t>45,71; 48,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>52,46; 54,91</t>
+          <t>52,55; 54,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53,76; 64,56</t>
+          <t>62,7; 65,07</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224306</t>
+          <t>247882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>193422</t>
+          <t>231687</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>417729</t>
+          <t>479569</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98787; 135267</t>
+          <t>98573; 133516</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>182297; 224142</t>
+          <t>183288; 223142</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>186683; 255943</t>
+          <t>214137; 277442</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>157600; 197345</t>
+          <t>159514; 199321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>189605; 227857</t>
+          <t>189816; 228562</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>170325; 217254</t>
+          <t>205558; 256456</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>265534; 322864</t>
+          <t>266753; 321955</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>383756; 438085</t>
+          <t>384292; 440620</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>374624; 460342</t>
+          <t>432557; 514847</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>259375</t>
+          <t>303818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>294259</t>
+          <t>338521</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>553634</t>
+          <t>642339</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>197299; 245324</t>
+          <t>196276; 244683</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>292762; 341049</t>
+          <t>294119; 340868</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>231784; 282906</t>
+          <t>276430; 330301</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>289526; 342246</t>
+          <t>287978; 338167</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>293579; 339016</t>
+          <t>293103; 340461</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>177127; 348301</t>
+          <t>314861; 359736</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>498657; 571383</t>
+          <t>500078; 573355</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>602771; 669100</t>
+          <t>604309; 667936</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>420786; 608400</t>
+          <t>608210; 675752</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>327784</t>
+          <t>382352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>345818</t>
+          <t>397210</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>673601</t>
+          <t>779562</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>247380; 302578</t>
+          <t>251240; 301886</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>295236; 347590</t>
+          <t>293970; 348475</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>304974; 351745</t>
+          <t>356559; 407595</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>319230; 372599</t>
+          <t>319557; 373268</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>340639; 388847</t>
+          <t>339386; 386432</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>328775; 365505</t>
+          <t>376811; 417638</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>582503; 665301</t>
+          <t>579579; 659308</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>648153; 720051</t>
+          <t>646013; 718513</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>640550; 699793</t>
+          <t>743331; 811515</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>431562</t>
+          <t>471031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>444882</t>
+          <t>487425</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>876444</t>
+          <t>958457</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>255505; 309739</t>
+          <t>253500; 304967</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>318482; 373339</t>
+          <t>320420; 371511</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>185285; 608129</t>
+          <t>447728; 497623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>309686; 363232</t>
+          <t>308316; 361087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>353757; 403804</t>
+          <t>353243; 402952</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>362197; 474822</t>
+          <t>466542; 505950</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>577547; 654255</t>
+          <t>579432; 654144</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>688423; 761923</t>
+          <t>687814; 765067</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>533755; 1052195</t>
+          <t>925148; 990210</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>367591</t>
+          <t>399112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>351001</t>
+          <t>391918</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>718593</t>
+          <t>791031</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>238444; 281656</t>
+          <t>241376; 282332</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>277067; 321889</t>
+          <t>276036; 319884</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>345355; 386316</t>
+          <t>375979; 421956</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>228384; 272411</t>
+          <t>226849; 273965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>232383; 278130</t>
+          <t>233181; 280165</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>333108; 366595</t>
+          <t>373734; 410337</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>482117; 544632</t>
+          <t>483641; 543414</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>522010; 587305</t>
+          <t>523482; 589566</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>690725; 744489</t>
+          <t>762926; 819666</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276617</t>
+          <t>306151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>465125</t>
+          <t>282186</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>741742</t>
+          <t>588337</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>195597; 229881</t>
+          <t>195586; 229291</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>191115; 227031</t>
+          <t>190550; 227392</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>264041; 289918</t>
+          <t>290410; 320468</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>163846; 201408</t>
+          <t>163515; 202507</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>188760; 229748</t>
+          <t>191754; 227050</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>386336; 551139</t>
+          <t>265304; 296759</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>369657; 423049</t>
+          <t>367772; 422865</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>391862; 447203</t>
+          <t>394119; 448787</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>671903; 859020</t>
+          <t>567883; 608994</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177424</t>
+          <t>195543</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>173296</t>
+          <t>188721</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>350720</t>
+          <t>384265</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>140910; 174043</t>
+          <t>141641; 173798</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>127446; 155563</t>
+          <t>126262; 156525</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>164020; 190236</t>
+          <t>181480; 208676</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129887; 168353</t>
+          <t>128954; 167956</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>137424; 181149</t>
+          <t>135747; 179949</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>159152; 186726</t>
+          <t>173635; 205599</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>279080; 330856</t>
+          <t>279502; 332746</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>270500; 326383</t>
+          <t>273261; 329087</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>329169; 370893</t>
+          <t>363274; 405527</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2064659</t>
+          <t>2305891</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2267802</t>
+          <t>2317668</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4332462</t>
+          <t>4623559</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1462378; 1587521</t>
+          <t>1468850; 1586102</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1779993; 1901186</t>
+          <t>1781020; 1895981</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1564500; 2246886</t>
+          <t>2243971; 2369034</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1698472; 1820255</t>
+          <t>1696677; 1819503</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1827756; 1954278</t>
+          <t>1833690; 1954092</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2131832; 2518286</t>
+          <t>2270890; 2373455</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3190779; 3370581</t>
+          <t>3190897; 3376370</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3639807; 3809963</t>
+          <t>3646552; 3812051</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3810020; 4575706</t>
+          <t>4534560; 4706158</t>
         </is>
       </c>
     </row>
